--- a/branches/feat-add-dmst-update-location/CodeSystem-mii-cs-meta-diz-standorte.xlsx
+++ b/branches/feat-add-dmst-update-location/CodeSystem-mii-cs-meta-diz-standorte.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-10-19</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat-add-dmst-update-location/CodeSystem-mii-cs-meta-diz-standorte.xlsx
+++ b/branches/feat-add-dmst-update-location/CodeSystem-mii-cs-meta-diz-standorte.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="217">
   <si>
     <t>Property</t>
   </si>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>52</t>
+    <t>53</t>
   </si>
   <si>
     <t>Code</t>
@@ -605,6 +605,12 @@
   </si>
   <si>
     <t>Tübingen</t>
+  </si>
+  <si>
+    <t>UKT-FLAME</t>
+  </si>
+  <si>
+    <t>Universitätsklinikum Tübingen - FLAME</t>
   </si>
   <si>
     <t>UKU</t>
@@ -1130,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1788,7 +1794,7 @@
         <v>198</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48">
@@ -1796,13 +1802,13 @@
         <v>71</v>
       </c>
       <c r="B48" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="C48" t="s" s="2">
+      <c r="D48" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="D48" t="s" s="2">
-        <v>202</v>
       </c>
     </row>
     <row r="49">
@@ -1810,13 +1816,13 @@
         <v>71</v>
       </c>
       <c r="B49" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C49" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="C49" t="s" s="2">
+      <c r="D49" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="D49" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="50">
@@ -1824,12 +1830,14 @@
         <v>71</v>
       </c>
       <c r="B50" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="C50" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="C50" t="s" s="2">
+      <c r="D50" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="D50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
@@ -1841,9 +1849,7 @@
       <c r="C51" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="D51" t="s" s="2">
-        <v>141</v>
-      </c>
+      <c r="D51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
@@ -1856,7 +1862,7 @@
         <v>211</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>212</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53">
@@ -1864,12 +1870,26 @@
         <v>71</v>
       </c>
       <c r="B53" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="C53" t="s" s="2">
+      <c r="D53" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="D53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="D54" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
